--- a/datos/gastos_demo.xlsx
+++ b/datos/gastos_demo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gastos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gastos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Comida con el director de compras de Torrelaya Sistemas para cerrar la renovación del contrato; dos comensales</t>
+          <t>Comida con el director de compras de Quintanavera Soluciones para cerrar la renovación del contrato; dos comensales</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">

--- a/datos/gastos_demo.xlsx
+++ b/datos/gastos_demo.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -506,17 +506,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Marta Gil</t>
+          <t>Jorge Sanz</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>alojamiento</t>
+          <t>representación</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Hotel una noche durante TECMA Feria Internacional del Urbanismo y Medio Ambiente en IFEMA</t>
+          <t>Cena de trabajo con el equipo de Indra en Teatro Kapital; cuatro comensales</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -551,12 +551,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jorge Sanz</t>
+          <t>Clara Vega</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Cena de trabajo con el equipo de Indra en Teatro Kapital; cuatro comensales</t>
+          <t>Comida de trabajo en Arzak con el responsable de operaciones de Mercadona; dos comensales</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Luis Pardo</t>
+          <t>Marta Gil</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -611,11 +611,11 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Bilbao</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>246</v>
+        <v>140</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Comida con dos responsables de compras de Iberdrola en Sobrino de Botín; tres comensales</t>
+          <t>Comida con el director de compras de Quintanavera Soluciones para cerrar la renovación del contrato; dos comensales</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -641,12 +641,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Clara Vega</t>
+          <t>Luis Pardo</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -656,11 +656,11 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Comida de trabajo en Arzak con el responsable de operaciones de Mercadona; dos comensales</t>
+          <t>Comida con el equipo de Telefónica para revisar el plan anual; dos comensales</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Jorge Sanz</t>
+          <t>Luis Ríos</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>transporte</t>
+          <t>representación</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>89</v>
+        <v>300</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Billete de tren Madrid-Barcelona en clase turista trayecto de ida</t>
+          <t>Cena con clientes en un bar nocturno de Málaga con motivo de TECMA, feria de Madrid; cuatro comensales</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -736,21 +736,21 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>representación</t>
+          <t>alojamiento</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Bilbao</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>140</v>
+        <v>210</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Comida con el director de compras de Quintanavera Soluciones para cerrar la renovación del contrato; dos comensales</t>
+          <t>Hotel una noche durante TECMA Feria Internacional del Urbanismo y Medio Ambiente en IFEMA</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -776,26 +776,26 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Clara Vega</t>
+          <t>Luis Pardo</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>dietas</t>
+          <t>representación</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Madrid</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>38</v>
+        <v>246</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Cena individual durante desplazamiento a Sevilla</t>
+          <t>Comida con dos responsables de compras de Iberdrola en Sobrino de Botín; tres comensales</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -821,26 +821,26 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Luis Pardo</t>
+          <t>Jorge Sanz</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>representación</t>
+          <t>transporte</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Madrid</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -849,10 +849,55 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Comida con el equipo de Telefónica para revisar el plan anual; dos comensales</t>
+          <t>Billete de tren Madrid-Barcelona en clase turista trayecto de ida</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>G-09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Clara Vega</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>dietas</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>38</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Cena individual durante desplazamiento a Sevilla</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>S</t>
         </is>
